--- a/ARM Functions/Item Edits/Mega Stone Pixilate.xlsx
+++ b/ARM Functions/Item Edits/Mega Stone Pixilate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\Item Edits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41FEE61F-89AA-4A6A-ADB5-1F4C6C0757AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A438290-2D8C-4BC3-9D71-1F59192093B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16457" windowHeight="17914" xr2:uid="{6B563214-6527-4E5F-B5EA-E821D6DED3A7}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>notes</t>
   </si>
@@ -99,12 +99,6 @@
     <t>bl 0x00092298</t>
   </si>
   <si>
-    <t>ldrh r0, [r0, 0xC]</t>
-  </si>
-  <si>
-    <t>BC00D0E1</t>
-  </si>
-  <si>
     <t>0F402DE9</t>
   </si>
   <si>
@@ -126,69 +120,18 @@
     <t>mov r1, r2</t>
   </si>
   <si>
-    <t>get species</t>
-  </si>
-  <si>
-    <t>get table</t>
-  </si>
-  <si>
-    <t>0020A0E3</t>
-  </si>
-  <si>
-    <t>mov r2, 0x0</t>
-  </si>
-  <si>
-    <t>B23091E1</t>
-  </si>
-  <si>
-    <t>ldrh r3, [r1, r2]</t>
-  </si>
-  <si>
-    <t>030050E1</t>
-  </si>
-  <si>
-    <t>cmp r0, r3</t>
-  </si>
-  <si>
-    <t>0300000A</t>
-  </si>
-  <si>
-    <t>000050E3</t>
-  </si>
-  <si>
-    <t>cmp r0, 0x0</t>
-  </si>
-  <si>
-    <t>022082E2</t>
-  </si>
-  <si>
-    <t>add r2, r2, 0x2</t>
-  </si>
-  <si>
-    <t>F8FFFFEA</t>
-  </si>
-  <si>
     <t>0F40BDE8</t>
   </si>
   <si>
     <t>0F80BDE8</t>
   </si>
   <si>
-    <t>Table</t>
-  </si>
-  <si>
     <t>000D4BF8</t>
   </si>
   <si>
     <t>Mega Stone Pixilate 0x2D/0x47/0xA4</t>
   </si>
   <si>
-    <t>0014AFA0</t>
-  </si>
-  <si>
-    <t>Absol</t>
-  </si>
-  <si>
     <t>mov r1, 0x3</t>
   </si>
   <si>
@@ -213,28 +156,34 @@
     <t>000DE73C</t>
   </si>
   <si>
-    <t>Table of valid Pokemon</t>
-  </si>
-  <si>
     <t>D2CEFEEB</t>
   </si>
   <si>
-    <t>34109FE5</t>
-  </si>
-  <si>
-    <t>0600000A</t>
-  </si>
-  <si>
     <t>470059E3</t>
   </si>
   <si>
-    <t>D3E9FF0A</t>
-  </si>
-  <si>
-    <t>0FDFFF3A</t>
-  </si>
-  <si>
-    <t>5BEBFF8A</t>
+    <t>bl 0x000D6F98</t>
+  </si>
+  <si>
+    <t>cmp r0, 0x1</t>
+  </si>
+  <si>
+    <t>11E2FFEB</t>
+  </si>
+  <si>
+    <t>010050E3</t>
+  </si>
+  <si>
+    <t>0400001A</t>
+  </si>
+  <si>
+    <t>DAE9FF0A</t>
+  </si>
+  <si>
+    <t>16DFFF3A</t>
+  </si>
+  <si>
+    <t>62EBFF8A</t>
   </si>
 </sst>
 </file>
@@ -639,7 +588,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B45B0BF-76E7-4635-9005-9D6B1877FAE8}">
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr defaultRowHeight="15.9"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="2"/>
@@ -676,14 +625,14 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="B3" s="2" t="str">
         <f>_xlfn.CONCAT("0",RIGHT(C3,1),"10A0E3")</f>
         <v>0310A0E3</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="D3" s="1"/>
     </row>
@@ -741,18 +690,18 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -761,25 +710,25 @@
         <v>000DE740</v>
       </c>
       <c r="B11" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>17</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="5" t="str">
-        <f t="shared" ref="A12:A30" si="1">DEC2HEX(HEX2DEC(A11)+4,8)</f>
+        <f t="shared" ref="A12:A22" si="1">DEC2HEX(HEX2DEC(A11)+4,8)</f>
         <v>000DE744</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D12" s="5"/>
     </row>
@@ -789,7 +738,7 @@
         <v>000DE748</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>12</v>
@@ -802,29 +751,23 @@
         <v>000DE74C</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>22</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="D14" s="4"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="str">
         <f t="shared" si="1"/>
         <v>000DE750</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C15" s="2" t="str">
-        <f>_xlfn.CONCAT("ldr r1, [pc, #",HEX2DEC(A30)-HEX2DEC(A15)-8,"]")</f>
-        <v>ldr r1, [pc, #52]</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>23</v>
+      <c r="B15" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -833,10 +776,11 @@
         <v>000DE754</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>25</v>
+        <v>38</v>
+      </c>
+      <c r="C16" s="2" t="str">
+        <f>_xlfn.CONCAT("bne 0x",A22)</f>
+        <v>bne 0x000DE76C</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -845,10 +789,11 @@
         <v>000DE758</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>27</v>
+        <v>20</v>
+      </c>
+      <c r="C17" s="2" t="str">
+        <f>SUBSTITUTE(C10,"push","pop")</f>
+        <v>pop {r0, r1, r2, r3, lr}</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -857,10 +802,10 @@
         <v>000DE75C</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -869,11 +814,10 @@
         <v>000DE760</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C19" s="2" t="str">
-        <f>_xlfn.CONCAT("beq 0x",A24)</f>
-        <v>beq 0x000DE774</v>
+        <v>39</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -881,11 +825,14 @@
         <f t="shared" si="1"/>
         <v>000DE764</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>31</v>
+      <c r="B20" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -894,11 +841,13 @@
         <v>000DE768</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C21" s="2" t="str">
-        <f>_xlfn.CONCAT("beq 0x",A29)</f>
-        <v>beq 0x000DE788</v>
+        <v>41</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -906,354 +855,25 @@
         <f t="shared" si="1"/>
         <v>000DE76C</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>000DE770</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C23" s="2" t="str">
-        <f>_xlfn.CONCAT("b 0x",A17)</f>
-        <v>b 0x000DE758</v>
+      <c r="B22" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="2" t="str">
+        <f>SUBSTITUTE(C17,"lr","pc")</f>
+        <v>pop {r0, r1, r2, r3, pc}</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>000DE774</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C24" s="2" t="str">
-        <f>SUBSTITUTE(C10,"push","pop")</f>
-        <v>pop {r0, r1, r2, r3, lr}</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>000DE778</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>44</v>
-      </c>
+      <c r="A24" s="1"/>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>000DE77C</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>47</v>
-      </c>
+      <c r="C26" s="6"/>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>000DE780</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>45</v>
-      </c>
+      <c r="C27" s="6"/>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>000DE784</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>000DE788</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C29" s="2" t="str">
-        <f>SUBSTITUTE(C24,"lr","pc")</f>
-        <v>pop {r0, r1, r2, r3, pc}</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>000DE78C</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B33" s="2" t="str">
-        <f>RIGHT(E33,2)&amp;LEFT(E33,2)</f>
-        <v>6701</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D33" s="2">
-        <v>359</v>
-      </c>
-      <c r="E33" s="2" t="str">
-        <f>DEC2HEX(D33,4)</f>
-        <v>0167</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="2" t="str">
-        <f>DEC2HEX(HEX2DEC(A33)+2,8)</f>
-        <v>0014AFA2</v>
-      </c>
-      <c r="B34" s="2" t="str">
-        <f t="shared" ref="B34:B47" si="2">RIGHT(E34,2)&amp;LEFT(E34,2)</f>
-        <v>0000</v>
-      </c>
-      <c r="C34" s="6"/>
-      <c r="E34" s="2" t="str">
-        <f t="shared" ref="E34:E48" si="3">DEC2HEX(D34,4)</f>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="2" t="str">
-        <f t="shared" ref="A35:A48" si="4">DEC2HEX(HEX2DEC(A34)+2,8)</f>
-        <v>0014AFA4</v>
-      </c>
-      <c r="B35" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>0000</v>
-      </c>
-      <c r="C35" s="6"/>
-      <c r="E35" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0014AFA6</v>
-      </c>
-      <c r="B36" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>0000</v>
-      </c>
-      <c r="C36" s="6"/>
-      <c r="E36" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0014AFA8</v>
-      </c>
-      <c r="B37" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>0000</v>
-      </c>
-      <c r="E37" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0014AFAA</v>
-      </c>
-      <c r="B38" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>0000</v>
-      </c>
-      <c r="E38" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0014AFAC</v>
-      </c>
-      <c r="B39" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>0000</v>
-      </c>
-      <c r="E39" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0014AFAE</v>
-      </c>
-      <c r="B40" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>0000</v>
-      </c>
-      <c r="E40" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0014AFB0</v>
-      </c>
-      <c r="B41" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>0000</v>
-      </c>
-      <c r="E41" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0014AFB2</v>
-      </c>
-      <c r="B42" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>0000</v>
-      </c>
-      <c r="E42" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0014AFB4</v>
-      </c>
-      <c r="B43" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>0000</v>
-      </c>
-      <c r="E43" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0014AFB6</v>
-      </c>
-      <c r="B44" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>0000</v>
-      </c>
-      <c r="E44" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0014AFB8</v>
-      </c>
-      <c r="B45" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>0000</v>
-      </c>
-      <c r="E45" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0014AFBA</v>
-      </c>
-      <c r="B46" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>0000</v>
-      </c>
-      <c r="E46" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0014AFBC</v>
-      </c>
-      <c r="B47" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>0000</v>
-      </c>
-      <c r="E47" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0014AFBE</v>
-      </c>
-      <c r="B48" s="2" t="str">
-        <f t="shared" ref="B48" si="5">RIGHT(E48,2)&amp;LEFT(E48,2)</f>
-        <v>0000</v>
-      </c>
-      <c r="E48" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
+      <c r="C28" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
